--- a/Supplementary Information/S7 B Cell Bulk RNA-seq Libraries.xlsx
+++ b/Supplementary Information/S7 B Cell Bulk RNA-seq Libraries.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\rrms\bulk\final_assignment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\devin\Desktop\rrms\Supplementary Information\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F05E7E-79D4-4375-9131-55349B4ED6E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5686CF-F209-47A7-90F2-5E0935E879B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12173" yWindow="1972" windowWidth="21600" windowHeight="11333" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="26182" windowHeight="14407" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BULK" sheetId="1" r:id="rId1"/>
@@ -701,7 +701,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -718,6 +718,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -767,7 +773,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -784,6 +790,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1087,18 +1094,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H131"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
+    <col min="1" max="2" width="12" style="6" customWidth="1"/>
+    <col min="3" max="3" width="14" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20" style="6" customWidth="1"/>
+    <col min="5" max="5" width="8" style="6" customWidth="1"/>
+    <col min="6" max="6" width="11" style="6" customWidth="1"/>
+    <col min="7" max="7" width="28" style="6" customWidth="1"/>
+    <col min="8" max="8" width="22" style="6" customWidth="1"/>
+    <col min="9" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="13.15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1124,7 +1132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1150,7 +1158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>14</v>
       </c>
@@ -1176,7 +1184,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -1202,7 +1210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
@@ -1228,7 +1236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -1254,7 +1262,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>23</v>
       </c>
@@ -1280,7 +1288,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1306,7 +1314,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>26</v>
       </c>
@@ -1332,7 +1340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
@@ -1358,7 +1366,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
@@ -1384,7 +1392,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -1410,7 +1418,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
@@ -1436,7 +1444,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>35</v>
       </c>
@@ -1462,7 +1470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>37</v>
       </c>
@@ -1488,7 +1496,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>38</v>
       </c>
@@ -1514,7 +1522,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>40</v>
       </c>
@@ -1540,7 +1548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
@@ -1566,7 +1574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>43</v>
       </c>
@@ -1592,7 +1600,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>45</v>
       </c>
@@ -1618,7 +1626,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>47</v>
       </c>
@@ -1644,7 +1652,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>49</v>
       </c>
@@ -1670,7 +1678,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>50</v>
       </c>
@@ -1696,7 +1704,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>53</v>
       </c>
@@ -1722,7 +1730,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -1748,7 +1756,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>56</v>
       </c>
@@ -1774,7 +1782,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>57</v>
       </c>
@@ -1800,7 +1808,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>59</v>
       </c>
@@ -1826,7 +1834,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>60</v>
       </c>
@@ -1852,7 +1860,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>62</v>
       </c>
@@ -1878,7 +1886,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>63</v>
       </c>
@@ -1904,7 +1912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>65</v>
       </c>
@@ -1930,7 +1938,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>66</v>
       </c>
@@ -1956,7 +1964,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>69</v>
       </c>
@@ -1982,7 +1990,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>71</v>
       </c>
@@ -2008,7 +2016,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>72</v>
       </c>
@@ -2034,7 +2042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>74</v>
       </c>
@@ -2060,7 +2068,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="4" t="s">
         <v>75</v>
       </c>
@@ -2086,7 +2094,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>78</v>
       </c>
@@ -2112,7 +2120,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="4" t="s">
         <v>80</v>
       </c>
@@ -2138,7 +2146,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>81</v>
       </c>
@@ -2164,7 +2172,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="4" t="s">
         <v>84</v>
       </c>
@@ -2190,7 +2198,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>85</v>
       </c>
@@ -2216,7 +2224,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>87</v>
       </c>
@@ -2242,7 +2250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>89</v>
       </c>
@@ -2268,7 +2276,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>91</v>
       </c>
@@ -2294,7 +2302,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
@@ -2320,7 +2328,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>94</v>
       </c>
@@ -2346,7 +2354,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>96</v>
       </c>
@@ -2372,7 +2380,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>97</v>
       </c>
@@ -2398,7 +2406,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>99</v>
       </c>
@@ -2424,7 +2432,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>101</v>
       </c>
@@ -2450,7 +2458,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>102</v>
       </c>
@@ -2476,7 +2484,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>104</v>
       </c>
@@ -2502,7 +2510,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>105</v>
       </c>
@@ -2528,7 +2536,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>107</v>
       </c>
@@ -2554,7 +2562,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>108</v>
       </c>
@@ -2580,7 +2588,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>110</v>
       </c>
@@ -2606,7 +2614,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>112</v>
       </c>
@@ -2632,7 +2640,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>113</v>
       </c>
@@ -2658,7 +2666,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>115</v>
       </c>
@@ -2684,7 +2692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>117</v>
       </c>
@@ -2710,7 +2718,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>118</v>
       </c>
@@ -2736,7 +2744,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>120</v>
       </c>
@@ -2762,7 +2770,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>121</v>
       </c>
@@ -2788,7 +2796,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>123</v>
       </c>
@@ -2814,7 +2822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>124</v>
       </c>
@@ -2840,7 +2848,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>126</v>
       </c>
@@ -2866,7 +2874,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>127</v>
       </c>
@@ -2892,7 +2900,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>129</v>
       </c>
@@ -2918,7 +2926,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>131</v>
       </c>
@@ -2944,7 +2952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>224</v>
       </c>
@@ -2970,7 +2978,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>132</v>
       </c>
@@ -2996,7 +3004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>133</v>
       </c>
@@ -3022,7 +3030,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>134</v>
       </c>
@@ -3048,7 +3056,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>136</v>
       </c>
@@ -3074,7 +3082,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>137</v>
       </c>
@@ -3100,7 +3108,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>139</v>
       </c>
@@ -3126,7 +3134,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>140</v>
       </c>
@@ -3152,7 +3160,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>142</v>
       </c>
@@ -3178,7 +3186,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>144</v>
       </c>
@@ -3204,7 +3212,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>146</v>
       </c>
@@ -3230,7 +3238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>147</v>
       </c>
@@ -3256,7 +3264,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>149</v>
       </c>
@@ -3282,7 +3290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>150</v>
       </c>
@@ -3308,7 +3316,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>151</v>
       </c>
@@ -3334,7 +3342,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>153</v>
       </c>
@@ -3360,7 +3368,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>154</v>
       </c>
@@ -3386,7 +3394,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>156</v>
       </c>
@@ -3412,7 +3420,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>157</v>
       </c>
@@ -3438,7 +3446,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>159</v>
       </c>
@@ -3464,7 +3472,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>160</v>
       </c>
@@ -3490,7 +3498,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>162</v>
       </c>
@@ -3516,7 +3524,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>164</v>
       </c>
@@ -3542,7 +3550,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>165</v>
       </c>
@@ -3568,7 +3576,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>167</v>
       </c>
@@ -3594,7 +3602,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>168</v>
       </c>
@@ -3620,7 +3628,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>170</v>
       </c>
@@ -3646,7 +3654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>172</v>
       </c>
@@ -3672,7 +3680,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>173</v>
       </c>
@@ -3698,7 +3706,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>175</v>
       </c>
@@ -3724,7 +3732,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>176</v>
       </c>
@@ -3750,7 +3758,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>178</v>
       </c>
@@ -3776,7 +3784,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>179</v>
       </c>
@@ -3802,7 +3810,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>181</v>
       </c>
@@ -3828,7 +3836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>182</v>
       </c>
@@ -3854,7 +3862,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>184</v>
       </c>
@@ -3880,7 +3888,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>186</v>
       </c>
@@ -3906,7 +3914,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>187</v>
       </c>
@@ -3932,7 +3940,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>189</v>
       </c>
@@ -3958,7 +3966,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>190</v>
       </c>
@@ -3984,7 +3992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>192</v>
       </c>
@@ -4010,7 +4018,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>193</v>
       </c>
@@ -4036,7 +4044,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>195</v>
       </c>
@@ -4062,7 +4070,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>196</v>
       </c>
@@ -4088,7 +4096,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>198</v>
       </c>
@@ -4114,7 +4122,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>199</v>
       </c>
@@ -4140,7 +4148,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>201</v>
       </c>
@@ -4166,7 +4174,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>202</v>
       </c>
@@ -4192,7 +4200,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>204</v>
       </c>
@@ -4218,7 +4226,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>205</v>
       </c>
@@ -4244,7 +4252,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>208</v>
       </c>
@@ -4270,7 +4278,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>209</v>
       </c>
@@ -4296,7 +4304,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>211</v>
       </c>
@@ -4322,7 +4330,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>212</v>
       </c>
@@ -4348,7 +4356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>214</v>
       </c>
@@ -4374,7 +4382,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>215</v>
       </c>
@@ -4400,7 +4408,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>217</v>
       </c>
@@ -4426,7 +4434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129" s="4" t="s">
         <v>218</v>
       </c>
@@ -4452,7 +4460,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>220</v>
       </c>
@@ -4478,7 +4486,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131" s="4" t="s">
         <v>222</v>
       </c>
